--- a/manual.xlsx
+++ b/manual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메뉴정의서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선택조건_CH-07" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적합성진단_CH-01" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="메뉴정의서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Index" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="개정이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="선택조건_CH-07" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="적합성진단_CH-01" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'메뉴정의서'!$A$4:$O$64</definedName>
@@ -853,11 +853,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>60개 화면(업무 52 + 공통 8) · v3.6 · 메뉴명=공개 사이트맵 확인 / 공통(CM)=프로토타입 v3.6 반영 / 회색 글씨 항목=추정(로그인 화면 미확인) / 메뉴ID: 업무코드-번호 (CM 공통 · MY · CT · PY · PM · CH · LN · CF · CS 서류·안내)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>60개 화면(업무 52 + 공통 8) · v3.7 · 메뉴명=공개 사이트맵 확인 / 공통(CM)=프로토타입 v3.7 반영 / 회색 글씨 항목=추정(로그인 화면 미확인) / 메뉴ID: 업무코드-번호 (CM 공통 · MY · CT · PY · PM · CH · LN · CF · CS 서류·안내)</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1008,7 +1007,7 @@
       </c>
       <c r="O5" s="34" t="inlineStr">
         <is>
-          <t>모바일 비로그인 시 로그인 박스 미노출(상단 로그인 버튼 이용) / v3.5: 모바일(860px 이하) 접속 시 「이럴 땐 이렇게」 미노출 / 공지사항: 「더보기」 또는 게시글 선택 시 공지사항 게시판 레이어팝업(우측 상단 X 닫기·Esc) — 글 선택 시 아래로 아코디언 펼침·다시 선택 시 접힘(한 번에 1건), 메인에서 게시글 선택 시 해당 글이 펼쳐진 상태로 열림</t>
+          <t>모바일 비로그인 시 로그인 박스 미노출(상단 로그인 버튼 이용) / v3.5: 모바일(860px 이하) 접속 시 「이럴 땐 이렇게」 미노출 / 공지사항: 「더보기」 또는 게시글 선택 시 공지사항 게시판 레이어팝업(우측 상단 X 닫기·Esc) — 글 선택 시 아래로 아코디언 펼침·다시 선택 시 접힘(한 번에 1건), 메인에서 게시글 선택 시 해당 글이 펼쳐진 상태로 열림 / v3.7: 내 보험 요약 「대출 잔액」은 보유 계약 대출 잔액 합계로 표시</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1392,7 @@
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>상단 [가가] 버튼. 설정은 해당 브라우저에 저장</t>
+          <t>상단 [가가] 버튼. 설정은 해당 브라우저에 저장 / v3.7: 큰글씨 전환 시 입력 중인 값·필수 동의 체크 유지</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2786,7 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>보완서류 이미지</t>
+          <t>보완서류 이미지(1장 이상 필수)</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -2810,7 +2809,11 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O29" s="10" t="n"/>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 선택한 청구 건에 제출 반영(진행단계 → 처리중), 보완서류 미첨부 시 오류 안내 후 제출 불가</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -5811,7 +5814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7040,6 +7043,168 @@
       <c r="E47" s="11" t="inlineStr">
         <is>
           <t>MY-06(삭제), CM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>단일폼 변경(T4) 필수 동의 체크가 큰글씨모드 전환 후에도 유지되도록 수정 (화면에는 해제로 보이나 동의 없이 진행되던 오류)</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>업무 전체 T4 (PM-02 등), CM-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>큰글씨모드·기획정보 보기 전환 시 입력 중인 값 유지</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>CM-06, 업무 전체 T3·T4·T5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>보완서류 제출: 선택한 청구 건에 반영, 보완서류 1장 이상 첨부해야 제출(미첨부 시 오류 안내)</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>PY-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>메인 내 보험 요약 「대출 잔액」을 보유 계약 대출 잔액 합계로 표시(고정값 제거)</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>CM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입 메뉴 데이터를 메뉴정의서 기준으로 동기화 (메뉴ID 체계 SL- 제외·CS, 1Depth 「서류·안내」, 표시·입력정보·비고)</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입 기획정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입 공개 확인 주소: https://jongho-han.github.io/one-channel/ (main 반영 시 자동 배포)</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
